--- a/monily-package/Form_1065_Accrual_2025.xlsx
+++ b/monily-package/Form_1065_Accrual_2025.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>$29,275 in SPV Loan disbursements are loan receivables / equity investments — NOT P&amp;L expenses.</t>
+          <t>$4,275 in SPV Loan disbursements are loan receivables / equity investments — NOT P&amp;L expenses.</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B27" s="11" t="n">
-        <v>148704.81</v>
+        <v>137704.81</v>
       </c>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="5" t="n"/>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>4247.429508196722</v>
+        <v>15067.10163934426</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>34188.88</v>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>946.97</v>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>946.97</v>
@@ -1537,141 +1537,129 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>506c SPV Loan</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>*** RECLASSIFIED to Schedule L (Asset)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>4275</v>
-      </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="22" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="24" t="n">
-        <v>29275</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Line 20 (Other) — Insurance D&amp;O</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Line 20 (Other) — Insurance D&amp;O</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>18000</v>
+          <t>Line 20 (Other) — Marketing</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>7500</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>18000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Line 20 (Other) — Professional fees</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>6000</v>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="F8" s="15" t="n">
+        <v>7500</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>12000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Line 20 (Other) — Contractor labor</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>4000</v>
+          <t>Line 20 (Other) — Professional fees</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>6000</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>11500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>TPA (second line)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Line 20 (Other) — Marketing</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>7500</v>
+          <t>Line 20 (Other) — Admin/TPA</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>4500</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>7500</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ad Spend</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Line 20 (Other) — Marketing</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>5000</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>506c SPV Loan</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>*** RECLASSIFIED to Schedule L (Asset)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>4275</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="24" t="n">
+        <v>4275</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TPA (second line)</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Line 20 (Other) — Admin/TPA</t>
+          <t>Line 20 (Other) — Contractor labor</t>
         </is>
       </c>
       <c r="G12" s="15" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="13">
@@ -1741,7 +1729,7 @@
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="11" t="n">
-        <v>61950</v>
+        <v>50950</v>
       </c>
     </row>
     <row r="18">
@@ -1757,7 +1745,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="24" t="n">
-        <v>29275</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="19">
@@ -1773,7 +1761,7 @@
       <c r="F19" s="18" t="n"/>
       <c r="G19" s="18" t="n"/>
       <c r="H19" s="19" t="n">
-        <v>91225</v>
+        <v>55225</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2258,7 @@
         </is>
       </c>
       <c r="C32" s="15" t="n">
-        <v>148704.81</v>
+        <v>137704.81</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -2290,7 +2278,7 @@
         </is>
       </c>
       <c r="C33" s="19" t="n">
-        <v>148704.81</v>
+        <v>137704.81</v>
       </c>
       <c r="D33" s="20" t="inlineStr"/>
     </row>
@@ -2313,7 +2301,7 @@
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
@@ -2360,7 +2348,7 @@
         </is>
       </c>
       <c r="C40" s="15" t="n">
-        <v>11500</v>
+        <v>4000</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
@@ -2416,7 +2404,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="D43" s="10" t="inlineStr"/>
     </row>
@@ -2464,7 +2452,7 @@
         </is>
       </c>
       <c r="C46" s="15" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
@@ -2484,7 +2472,7 @@
         </is>
       </c>
       <c r="C47" s="19" t="n">
-        <v>148704.81</v>
+        <v>130204.81</v>
       </c>
       <c r="D47" s="20" t="inlineStr"/>
     </row>
@@ -2507,11 +2495,11 @@
         </is>
       </c>
       <c r="C50" s="22" t="n">
-        <v>29275</v>
+        <v>4275</v>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>Aug $4,275 + Oct $25,000 = $29,275. Loan receivables / SPV equity investment; appears on Schedule L (Tab 7), not Form 1065 Page 1.</t>
+          <t>Aug $4,275 (Oct $25K SPV disbursement was reclassified out of GP expenses entirely per Nairne 2026-05-07). Loan receivable / SPV equity investment — appears on Schedule L (Tab 7), not Form 1065 Page 1.</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2595,7 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -2901,7 +2889,7 @@
         </is>
       </c>
       <c r="C28" s="16" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
@@ -3058,7 +3046,7 @@
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
@@ -3380,7 +3368,7 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>4247.429508196722</v>
+        <v>15067.10163934426</v>
       </c>
       <c r="D28" s="21">
         <f> 98.3607% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
@@ -3623,7 +3611,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>4247.429508196722</v>
+        <v>15067.10163934426</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -3663,7 +3651,7 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>4247.429508196722</v>
+        <v>15067.10163934426</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -3681,14 +3669,14 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Box 1 amount ($4,247.43) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
+          <t>Box 1 amount ($15,067.10) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Box 14 ($4,247.43) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
+          <t>Box 14 ($15,067.10) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4034,7 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D28" s="21">
         <f> 0.8197% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
@@ -4289,7 +4277,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -4329,7 +4317,7 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -4347,14 +4335,14 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Box 1 amount ($35.40) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
+          <t>Box 1 amount ($125.56) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Box 14 ($35.40) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
+          <t>Box 14 ($125.56) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4700,7 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D28" s="21">
         <f> 0.8197% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
@@ -4955,7 +4943,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -4995,7 +4983,7 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -5013,14 +5001,14 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Box 1 amount ($35.40) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
+          <t>Box 1 amount ($125.56) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Box 14 ($35.40) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
+          <t>Box 14 ($125.56) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
         </is>
       </c>
     </row>
@@ -5347,11 +5335,11 @@
         <v>0</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>29275</v>
+        <v>4275</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>506c SPV Loan / Investment — $29,275.00 (Aug $4,275 + Oct $25,000). Reclassified from P&amp;L. ⚠️ Confirm whether loan receivable or equity investment.</t>
+          <t>506c SPV Loan / Investment — $4,275.00 (Aug $4,275 + Oct $25,000). Reclassified from P&amp;L. ⚠️ Confirm whether loan receivable or equity investment.</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>39775</v>
+        <v>14775</v>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
@@ -5715,7 +5703,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="15" t="n">
-        <v>-31764.6</v>
+        <v>-20764.6</v>
       </c>
       <c r="E38" s="10">
         <f> Net Income for the year − Cumulative Distributions. ⚠️ Add any member capital contributions.</f>
@@ -5737,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>-31764.6</v>
+        <v>-20764.6</v>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
@@ -5762,7 +5750,7 @@
     <row r="45" ht="35" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Total Assets shown ($39,775.00) excludes cash. Once Cash + member capital contributions are filled in, the sheet should balance.</t>
+          <t>Total Assets shown ($14,775.00) excludes cash. Once Cash + member capital contributions are filled in, the sheet should balance.</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5856,7 @@
         </is>
       </c>
       <c r="C6" s="15" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -5936,7 +5924,7 @@
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
     </row>
@@ -6000,7 +5988,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>4318.220000000001</v>
+        <v>15318.22</v>
       </c>
       <c r="D14" s="21">
         <f> Line 5 − Line 8. Should match Schedule K Line 1.</f>
@@ -6031,7 +6019,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>The 506c SPV reclassification ($29,275 from P&amp;L to balance sheet) is reflected in BOTH books and tax — no M-1 adjustment needed.</t>
+          <t>The 506c SPV reclassification ($4,275 from P&amp;L to balance sheet) is reflected in BOTH books and tax — no M-1 adjustment needed.</t>
         </is>
       </c>
     </row>
@@ -6184,13 +6172,13 @@
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>4247.429508196722</v>
+        <v>15067.10163934426</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
     </row>
     <row r="10">
@@ -6226,13 +6214,13 @@
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>4247.429508196722</v>
+        <v>15067.10163934426</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>35.39524590163936</v>
+        <v>125.5591803278689</v>
       </c>
     </row>
     <row r="12">
@@ -6310,13 +6298,13 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>-29941.45049180328</v>
+        <v>-19121.77836065574</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>-911.5747540983607</v>
+        <v>-821.4108196721312</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>-911.5747540983607</v>
+        <v>-821.4108196721312</v>
       </c>
     </row>
     <row r="18">
@@ -6329,21 +6317,21 @@
     <row r="19" ht="35" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Nairne ending capital: $-29,941.45 (BEFORE any 2025 capital contributions)</t>
+          <t>Nairne ending capital: $-19,121.78 (BEFORE any 2025 capital contributions)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Raj ending capital: $-911.57 (BEFORE any 2025 capital contributions)</t>
+          <t>Raj ending capital: $-821.41 (BEFORE any 2025 capital contributions)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Phil ending capital: $-911.57 (BEFORE any 2025 capital contributions)</t>
+          <t>Phil ending capital: $-821.41 (BEFORE any 2025 capital contributions)</t>
         </is>
       </c>
     </row>

--- a/monily-package/Form_1065_Accrual_2025.xlsx
+++ b/monily-package/Form_1065_Accrual_2025.xlsx
@@ -892,11 +892,11 @@
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>98.3607%</t>
+          <t>96.8000%</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>15067.10163934426</v>
+        <v>14828.03696</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>34188.88</v>
@@ -910,11 +910,11 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>0.8197%</t>
+          <t>1.6000%</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>946.97</v>
@@ -928,11 +928,11 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>0.8197%</t>
+          <t>1.6000%</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D34" s="14" t="n">
         <v>946.97</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Schedule K-1 for Nairne (60%)</t>
+          <t>Schedule K-1 for Nairne (30.25% economic / 96.80% normalized)</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>Allocated to partners per ownership: Nairne 98.36%, Raj 0.82%, Phil 0.82%</t>
+          <t>Allocated to partners per ownership: Nairne 96.80%, Raj 1.60%, Phil 1.60% (per Nairne 2026-05-07 — 50%×Fund Mgmt to AJ as 1099)</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Partner: Nairne  |  Ownership: 98.3607%</t>
+          <t>Partner: Nairne  |  Ownership: 96.8000%</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>98.3607%</t>
+          <t>96.8000%</t>
         </is>
       </c>
     </row>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>15067.10163934426</v>
+        <v>14828.03696</v>
       </c>
       <c r="D28" s="21">
-        <f> 98.3607% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
+        <f> 96.8000% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
         <v/>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>15067.10163934426</v>
+        <v>14828.03696</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>15067.10163934426</v>
+        <v>14828.03696</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -3669,14 +3669,14 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Box 1 amount ($15,067.10) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
+          <t>Box 1 amount ($14,828.04) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Box 14 ($15,067.10) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
+          <t>Box 14 ($14,828.04) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Partner: Raj Duggal  |  Ownership: 0.8197%</t>
+          <t>Partner: Raj Duggal  |  Ownership: 1.6000%</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.8197%</t>
+          <t>1.6000%</t>
         </is>
       </c>
     </row>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D28" s="21">
-        <f> 0.8197% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
+        <f> 1.6000% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
         <v/>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -4335,14 +4335,14 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Box 1 amount ($125.56) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
+          <t>Box 1 amount ($245.09) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Box 14 ($125.56) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
+          <t>Box 14 ($245.09) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Partner: Phil  |  Ownership: 0.8197%</t>
+          <t>Partner: Phil  |  Ownership: 1.6000%</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.8197%</t>
+          <t>1.6000%</t>
         </is>
       </c>
     </row>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D28" s="21">
-        <f> 0.8197% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
+        <f> 1.6000% of partnership ordinary income (Form 1065 Line 22). Reported on Schedule E Part II of partner's 1040.</f>
         <v/>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -5001,14 +5001,14 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Box 1 amount ($125.56) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
+          <t>Box 1 amount ($245.09) is ordinary income. Add to your Schedule E Part II, then to your 1040 Line 8.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Box 14 ($125.56) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
+          <t>Box 14 ($245.09) is subject to Self-Employment Tax (Schedule SE) if you're an active managing member.</t>
         </is>
       </c>
     </row>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>15067.10163934426</v>
+        <v>14828.03696</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
     </row>
     <row r="10">
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>15067.10163934426</v>
+        <v>14828.03696</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>125.5591803278689</v>
+        <v>245.09152</v>
       </c>
     </row>
     <row r="12">
@@ -6298,13 +6298,13 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>-19121.77836065574</v>
+        <v>-19360.84304</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>-821.4108196721312</v>
+        <v>-701.87848</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>-821.4108196721312</v>
+        <v>-701.87848</v>
       </c>
     </row>
     <row r="18">
@@ -6317,21 +6317,21 @@
     <row r="19" ht="35" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Nairne ending capital: $-19,121.78 (BEFORE any 2025 capital contributions)</t>
+          <t>Nairne ending capital: $-19,360.84 (BEFORE any 2025 capital contributions)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Raj ending capital: $-821.41 (BEFORE any 2025 capital contributions)</t>
+          <t>Raj ending capital: $-701.88 (BEFORE any 2025 capital contributions)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Phil ending capital: $-821.41 (BEFORE any 2025 capital contributions)</t>
+          <t>Phil ending capital: $-701.88 (BEFORE any 2025 capital contributions)</t>
         </is>
       </c>
     </row>
